--- a/submissions/candeleroj98_methods_description_form_track2.xlsx
+++ b/submissions/candeleroj98_methods_description_form_track2.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Public sources only. The only patient-specific input is the gene-level, categorical extract of the Track 1 result (seven genes, no positions, alleles, genotype calls or read metrics); the Track 1 submission file is not in the repository. No dataset file (FASTQ, BAM, VCF) was given to any AI assistant. Data from the challenge will be deleted by 23 November 2026, within 30 days of the submission deadline, as the Official Rules require, and the deletion will be confirmed to the organisers by e-mail. Under the hackathon embargo, no peer-reviewed manuscript using the dataset will be submitted until the organisers publish a report or preprint. The submission, including code and derived outputs, is released under CC BY 4.0, as the terms of the dataset state (participant submissions and results, including predictions, code and reports, are released under CC BY 4.0 and may be reused with attribution) (the repository also carries an MIT licence file for the code, and tables with ChEMBL-derived fields are CC BY-SA 3.0). GitHub link: provided with the submission. All outputs are hypotheses for follow-up, not evidence of efficacy; only FDA-approved drugs are considered (71 of 71 drugs of the study confirmed in Drugs@FDA); the child's age is unknown and never assumed; no dosing or treatment recommendation is given.</t>
+          <t xml:space="preserve">Public sources only. The only patient-specific input is the gene-level, categorical extract of the Track 1 result (seven genes, no positions, alleles, genotype calls or read metrics); the Track 1 submission file is not in the repository. No dataset file (FASTQ, BAM, VCF) was given to any AI assistant. Data from the challenge will be deleted by 23 November 2026, within 30 days of the submission deadline, as the Official Rules require, and the deletion will be confirmed to the organisers by e-mail. Under the hackathon embargo, no peer-reviewed manuscript using the dataset will be submitted until the organisers publish a report or preprint. The submission, including code and derived outputs, is released under CC BY 4.0, as the terms of the dataset state (participant submissions and results, including predictions, code and reports, are released under CC BY 4.0 and may be reused with attribution) (the licence file of the repository is the CC BY 4.0 text, and tables with ChEMBL-derived fields are CC BY-SA 3.0). GitHub link: provided with the submission. All outputs are hypotheses for follow-up, not evidence of efficacy; only FDA-approved drugs are considered (71 of 71 drugs of the study confirmed in Drugs@FDA); the child's age is unknown and never assumed; no dosing or treatment recommendation is given.</t>
         </is>
       </c>
     </row>
